--- a/ricette.xlsx
+++ b/ricette.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Progetti_App\diete_gruppo_sanguigno\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FDB86788-05B9-4595-99D2-20C58AEEB152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E1B0A84-03D6-42D3-A8BB-DD7A30A419B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{180D6C7E-1573-4D38-AF23-D62180C2F3F7}"/>
   </bookViews>
@@ -39,15 +39,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="140">
   <si>
     <t>Gruppo</t>
   </si>
   <si>
     <t>Nome</t>
-  </si>
-  <si>
-    <t>Tempo</t>
   </si>
   <si>
     <t>Difficolta</t>
@@ -1016,19 +1013,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5881F81E-9AB6-4C4C-9823-133F37B8E232}">
-  <dimension ref="A1:G34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F34"/>
+  <sheetFormatPr defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.28515625" customWidth="1"/>
     <col min="2" max="2" width="49.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="127.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="99" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="109.140625" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="127.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="99" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="109.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1047,15 +1043,15 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>7</v>
       </c>
       <c r="D2" t="s">
@@ -1064,18 +1060,18 @@
       <c r="E2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="165" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>11</v>
       </c>
       <c r="D3" t="s">
@@ -1084,298 +1080,298 @@
       <c r="E3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="195" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>0</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
         <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="198" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>0</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
         <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
       </c>
       <c r="E5" t="s">
         <v>19</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="165" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>0</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
         <v>21</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
       </c>
       <c r="E6" t="s">
         <v>22</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="165" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>0</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
         <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
       </c>
       <c r="E7" t="s">
         <v>25</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="135" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>0</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
         <v>27</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
       </c>
       <c r="E8" t="s">
         <v>28</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="165" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>0</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
         <v>30</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
       </c>
       <c r="E9" t="s">
         <v>31</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
         <v>32</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>0</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
         <v>33</v>
-      </c>
-      <c r="D10" t="s">
-        <v>8</v>
       </c>
       <c r="E10" t="s">
         <v>34</v>
       </c>
       <c r="F10" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
         <v>35</v>
       </c>
-      <c r="G10" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="180" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>0</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" t="s">
         <v>36</v>
-      </c>
-      <c r="D11" t="s">
-        <v>12</v>
       </c>
       <c r="E11" t="s">
         <v>37</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
         <v>38</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="135" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>0</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s">
         <v>39</v>
-      </c>
-      <c r="D12" t="s">
-        <v>8</v>
       </c>
       <c r="E12" t="s">
         <v>40</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="150" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>0</v>
-      </c>
-      <c r="B13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" t="s">
+    <row r="14" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>0</v>
+      </c>
+      <c r="B14" t="s">
         <v>43</v>
       </c>
-      <c r="F13" t="s">
-        <v>29</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="150" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>0</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
         <v>44</v>
-      </c>
-      <c r="D14" t="s">
-        <v>8</v>
       </c>
       <c r="E14" t="s">
         <v>45</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>0</v>
+      </c>
+      <c r="B15" t="s">
         <v>46</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="135" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>0</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" t="s">
         <v>47</v>
-      </c>
-      <c r="D15" t="s">
-        <v>12</v>
       </c>
       <c r="E15" t="s">
         <v>48</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>0</v>
+      </c>
+      <c r="B16" t="s">
         <v>49</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="150" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>0</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" t="s">
         <v>50</v>
-      </c>
-      <c r="D16" t="s">
-        <v>12</v>
       </c>
       <c r="E16" t="s">
         <v>51</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>0</v>
+      </c>
+      <c r="B17" t="s">
         <v>52</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="255" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>0</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" t="s">
         <v>53</v>
-      </c>
-      <c r="D17" t="s">
-        <v>12</v>
       </c>
       <c r="E17" t="s">
         <v>54</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>0</v>
+      </c>
+      <c r="B18" t="s">
         <v>55</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="210" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>0</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>56</v>
       </c>
       <c r="D18" t="s">
@@ -1384,331 +1380,328 @@
       <c r="E18" t="s">
         <v>58</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>0</v>
+      </c>
+      <c r="B19" t="s">
         <v>59</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="180" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>0</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" t="s">
         <v>60</v>
-      </c>
-      <c r="D19" t="s">
-        <v>8</v>
       </c>
       <c r="E19" t="s">
         <v>61</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>0</v>
+      </c>
+      <c r="B20" t="s">
         <v>62</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>0</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" t="s">
         <v>63</v>
-      </c>
-      <c r="D20" t="s">
-        <v>12</v>
       </c>
       <c r="E20" t="s">
         <v>64</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>0</v>
+      </c>
+      <c r="B21" t="s">
         <v>65</v>
       </c>
-      <c r="G20" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="135" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>0</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" t="s">
         <v>66</v>
-      </c>
-      <c r="D21" t="s">
-        <v>12</v>
       </c>
       <c r="E21" t="s">
         <v>67</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>0</v>
+      </c>
+      <c r="B22" t="s">
         <v>68</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="150" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>0</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" t="s">
         <v>69</v>
-      </c>
-      <c r="D22" t="s">
-        <v>12</v>
       </c>
       <c r="E22" t="s">
         <v>70</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>0</v>
+      </c>
+      <c r="B23" t="s">
         <v>71</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="180" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>0</v>
-      </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" t="s">
         <v>72</v>
-      </c>
-      <c r="D23" t="s">
-        <v>12</v>
       </c>
       <c r="E23" t="s">
         <v>73</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>0</v>
+      </c>
+      <c r="B24" t="s">
         <v>74</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="210" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>0</v>
-      </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" t="s">
         <v>75</v>
-      </c>
-      <c r="D24" t="s">
-        <v>12</v>
       </c>
       <c r="E24" t="s">
         <v>76</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>0</v>
+      </c>
+      <c r="B25" t="s">
         <v>77</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="165" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>0</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" t="s">
         <v>78</v>
-      </c>
-      <c r="D25" t="s">
-        <v>12</v>
       </c>
       <c r="E25" t="s">
         <v>79</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>0</v>
+      </c>
+      <c r="B26" t="s">
         <v>80</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="120" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>0</v>
-      </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" t="s">
         <v>81</v>
-      </c>
-      <c r="D26" t="s">
-        <v>8</v>
       </c>
       <c r="E26" t="s">
         <v>82</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>0</v>
+      </c>
+      <c r="B27" t="s">
         <v>83</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="135" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>0</v>
-      </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" t="s">
         <v>84</v>
-      </c>
-      <c r="D27" t="s">
-        <v>8</v>
       </c>
       <c r="E27" t="s">
         <v>85</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>0</v>
+      </c>
+      <c r="B28" t="s">
         <v>86</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="135" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>0</v>
-      </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" t="s">
         <v>87</v>
-      </c>
-      <c r="D28" t="s">
-        <v>8</v>
       </c>
       <c r="E28" t="s">
         <v>88</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>0</v>
+      </c>
+      <c r="B29" t="s">
         <v>89</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="225" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>0</v>
-      </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" t="s">
         <v>90</v>
-      </c>
-      <c r="D29" t="s">
-        <v>8</v>
       </c>
       <c r="E29" t="s">
         <v>91</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30" t="s">
         <v>92</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="165" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>0</v>
-      </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" t="s">
         <v>93</v>
-      </c>
-      <c r="D30" t="s">
-        <v>12</v>
       </c>
       <c r="E30" t="s">
         <v>94</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>0</v>
+      </c>
+      <c r="B31" t="s">
         <v>95</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="135" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>0</v>
-      </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" t="s">
         <v>96</v>
-      </c>
-      <c r="D31" t="s">
-        <v>8</v>
       </c>
       <c r="E31" t="s">
         <v>97</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>0</v>
+      </c>
+      <c r="B32" t="s">
         <v>98</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="180" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>0</v>
-      </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" t="s">
         <v>99</v>
-      </c>
-      <c r="D32" t="s">
-        <v>12</v>
       </c>
       <c r="E32" t="s">
         <v>100</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>0</v>
+      </c>
+      <c r="B33" t="s">
         <v>101</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="240" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>0</v>
-      </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
+        <v>56</v>
+      </c>
+      <c r="D33" t="s">
         <v>102</v>
-      </c>
-      <c r="D33" t="s">
-        <v>57</v>
       </c>
       <c r="E33" t="s">
         <v>103</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>0</v>
+      </c>
+      <c r="B34" t="s">
         <v>104</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="135" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>0</v>
-      </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" t="s">
         <v>105</v>
-      </c>
-      <c r="D34" t="s">
-        <v>8</v>
       </c>
       <c r="E34" t="s">
         <v>106</v>
       </c>
-      <c r="F34" t="s">
-        <v>107</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>140</v>
+      <c r="F34" s="3" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/ricette.xlsx
+++ b/ricette.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Progetti_App\diete_gruppo_sanguigno\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E1B0A84-03D6-42D3-A8BB-DD7A30A419B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68DFC621-51AF-4975-8DED-652F3C18564C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{180D6C7E-1573-4D38-AF23-D62180C2F3F7}"/>
   </bookViews>
   <sheets>
-    <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/ricette.xlsx
+++ b/ricette.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Progetti_App\diete_gruppo_sanguigno\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62935346-C310-4E0F-9D1E-EC1B77423066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CA7F06A-200F-46C5-B152-1AB81D3A04A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="143">
   <si>
     <t>Gruppo</t>
   </si>
@@ -55,18 +55,6 @@
 </t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">farina di mandorle; uova; mela; cremor tartaro; scorza grattugiata di limone
-</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Sbucciare e grattugiare finemente la mela. Strizzarla con le mani per eliminare il liquido in eccesso. In una ciotola unire le uova, la farina di mandorle, la mela strizzata, il cremor tartaro e la scorza grattugiata di limone. Mescolare, energicamente, con una frusta da cucina fino a ottenere un impasto fluido e omogeneo. Ungere leggermente una padella antiaderente e scaldarla a fiamma dolce. Versare un un mestolino, o metà mestolo, di composto nella padella e cuocere a fuoco lento. Quando iniziano a comparire le prime bollicine in superficie, girare il pancake e proseguire la cottura dell’altro lato sino a doratura. </t>
   </si>
   <si>
@@ -77,9 +65,6 @@
   </si>
   <si>
     <t xml:space="preserve">150 gr di farina di ceci (denaturata); 150-180 ml di acqua; 2 uova; ½ cucchiaino di bicarbonato di sodio; un pizzico di sale; Olio extravergine di oliva q.b.  </t>
-  </si>
-  <si>
-    <t>farina di ceci; uova; bicarbonato di sodio; sale marino integrale; olio extravergine di oliva</t>
   </si>
   <si>
     <t>Disporre la farina di ceci denaturata in una ciotola, aggiungere un pizzico di sale e proseguire aggiungendo lentamente nell'acqua mentre si mescola con una frusta da cucina. Mescolare fino a ottenere una pastella liscia, senza grumi e lasciar riposare il composto per in frigo, ricoperto con pellicola da cucina o con un coperchio adatto.
@@ -114,25 +99,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">nocciole; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>datteri Medjoul; uova; caffè di cicoria; cioccolato fondente</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Tritare finemente le nocciole insieme ai datteri snocciolati utilizzando un comune minipimer o un piccolo tritatutto, fino a ottenere un composto omogeneo e denso. 
 Trasferire il tritato in una ciotola capiente, aggiungere le uova e montare accuratamente con una frusta a mano per alcuni minuti, fino a rendere il composto spumoso. Versare a filo il caffè e continuare a mescolare energicamente per circa un minuto per amalgamare tutti gli ingredienti.
 Versare il composto ottenuto in una teglia rettangolare precedentemente rivestita con carta da forno. Stendere la superficie in modo uniforme con una spatola e cuocere in forno preriscaldato a 160-170 °C per circa 15 minuti (regolandosi in base alla potenza del proprio forno).
@@ -161,27 +127,6 @@
         <charset val="1"/>
       </rPr>
       <t>15 gr cuticola di psillio; 400 ml di acqua tiepida; Due zucchine; 5 gr lievito secco; Una presa di sale marino integrale; Olio extravergine di oliva q.b. Spezie consentite</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">farina fave; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">cuticola di psillio; zucchine; lievito secco; sale marino integrale; Olio extravergine di oliva; </t>
     </r>
   </si>
   <si>
@@ -264,10 +209,6 @@
     <t xml:space="preserve">200 gr noci; 35 gr cioccolato fondente; 4 uova; 30 gr di zucchero; 12 pirottini  </t>
   </si>
   <si>
-    <t xml:space="preserve">Noci; cioccolato fondente; uova; zucchero 
-</t>
-  </si>
-  <si>
     <t>Tritare finemente le noci e il cioccolato fondente insieme utilizzando un comune tritatutto o un minipimer, fino a ottenere un composto sottile simile a una farina.
 Trasferire il trito ottenuto in una ciotola capiente, aggiungere lo zucchero e le uova, quindi montare accuratamente con una frusta a mano (o uno sbattitore elettrico) per un paio di minuti, finché il composto non risulterà ben amalgamato e leggermente spumoso.
 Disporre 12 pirottini di carta all'interno di uno stampo per muffin (o su una teglia da forno) e distribuire uniformemente il composto al loro interno, riempiendoli quasi del tutto.
@@ -281,10 +222,6 @@
     <t xml:space="preserve">300 gr di carote (pesate pulite e pelate); 100 gr di farina di mandorle; 100 gr di granella di nocciole; 80 gr di farina di grano saraceno; 3 uova; ½ cucchiaino (circa 3 gr) di bicarbonato di sodio; Un cucchiaino (circa 6 gr) di cremor tartaro; Aroma di vaniglia q.b. </t>
   </si>
   <si>
-    <t>Carote; farina di mandorle; granella di nocciole; farina di grano saraceno; uova
-bicarbonato di sodio; cremor tartaro; vaniglia</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pelare e spuntare le carote, quindi grattugiarle finemente con una grattugia a mano a fori stretti (o tritarle con un semplice tritatutto); se risultano particolarmente succose, tamponarle leggermente con della carta assorbente. 
 In una ciotola capiente, sgusciare le uova e montarle accuratamente con una frusta a mano per un paio di minuti, finché non diventeranno chiare e spumose. Unire alle uova le carote grattugiate e l'aroma di vaniglia, amalgamando delicatamente con una spatola. 
 A questo punto, incorporare la farina di mandorle, la granella di nocciole e la farina di grano saraceno, mescolando energicamente dal basso verso l'alto fino a ottenere un composto omogeneo e denso. Aggiungere infine il bicarbonato di sodio e il cremor tartaro (meglio se setacciati) e mescolare bene per distribuirli in modo uniforme nell'impasto. 
@@ -295,9 +232,6 @@
   </si>
   <si>
     <t>150 gr mandorle tostate; 100 gr uvetta sultanina; 150 ml albume; 20 pirottini piccoli di carta piccoli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mandorle tostate; uvetta sultanina; albume; </t>
   </si>
   <si>
     <t>Tritare finemente le mandorle insieme all'uvetta utilizzando un comune tritatutto o un minipimer, fino a ottenere un composto omogeneo e sminuzzato.
@@ -314,10 +248,6 @@
 Tre uova; 200 gr scarola; 200 gr tacchino a fette sottili (affettato o fesa arrostita)</t>
   </si>
   <si>
-    <t>farina di riso; Sale marino integrale; olio extravergine di oliva; acqua; uova; scarola
-Tacchino</t>
-  </si>
-  <si>
     <t>In una ciotola capiente, versare la farina di riso e una presa di sale marino integrale, quindi mescolare le polveri. Versare l'acqua a filo continuando a mescolare con una frusta a mano per evitare la formazione di grumi. Aggiungere le tre uova e un cucchiaio di olio extravergine di oliva, poi sbattere energicamente per circa tre minuti fino a ottenere una pastella liscia, fluida e ben amalgamata.
 Nel frattempo, rivestire una teglia da forno rettangolare con della carta da forno. Distribuire la scarola su tutta la base della teglia e versarvi sopra la pastella in modo uniforme.
 Cuocere in forno statico preriscaldato a 180 °C per 40 minuti.
@@ -331,9 +261,6 @@
     <t>150g yogurt; 100g ananas; Mandorle; Miele</t>
   </si>
   <si>
-    <t>yogurt, ananas, mandorle, miele</t>
-  </si>
-  <si>
     <t>Unire yogurt e ananas a cubetti. Aggiungere mandorle e miele. Mescolare e servire.</t>
   </si>
   <si>
@@ -343,9 +270,6 @@
     <t xml:space="preserve">75 gr di fagioli borlotti freschi (o altri legumi consentiti); 250 gr di macinato di manzo; Una carota e mezza
 ½ cipolla; Sedano q.b. 75 ml di vino bianco; Olio extravergine di oliva q.b. Sale marino integrale q.b.
 Bicarbonato </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Borlotti; manzo; carota; cipolla; sedano; vino bianco; Olio extravergine di oliva; Sale marino integrale; Bicarbonato </t>
   </si>
   <si>
     <t>Sciacquare i fagioli borlotti sotto acqua corrente e lasciarli in ammollo in una ciotola con acqua e un pizzico di bicarbonato per 30 minuti. Scolarli e risciacquarli molto bene.
@@ -362,9 +286,6 @@
 </t>
   </si>
   <si>
-    <t>farina di piselli; acqua; olio extravergine di oliva; Cipolla; Aglio in polvere; Sale marino integrale</t>
-  </si>
-  <si>
     <t>In una scodella capiente, versare la farina di piselli, il sale marino integrale, l'aglio in polvere e la cipolla in polvere (o la cipolla fresca tritata finissimamente). Mescolare bene le polveri e gli aromi con un cucchiaio.
 Aggiungere un filo di olio extravergine di oliva e continuare a mescolare. Versare l'acqua e amalgamare con cura fino a raggiungere una consistenza cremosa e leggermente appiccicosa.
 Preparare una teglia rettangolare rivestita con carta da forno leggermente oleata con olio extravergine.
@@ -378,9 +299,6 @@
     <t xml:space="preserve">180 gr di farina di mandorle; 190 gr di farina di amaranto; 80 gr di uvetta sultanina; 5 uova intere </t>
   </si>
   <si>
-    <t xml:space="preserve">Mandorle; amaranto; uvetta sultanina; uova </t>
-  </si>
-  <si>
     <t>In una ciotola capiente, versare la farina di mandorle e la farina di amaranto, mescolandole bene tra loro con una forchetta per amalgamare le polveri.
 Aggiungere l'uvetta sultanina e continuare a mescolare. Versare infine le uova intere (precedentemente leggermente sbattute a parte per amalgamarle) e lavorare il tutto con una frusta a mano o una spatola per circa un minuto, finché non si otterrà un impasto denso, omogeneo e leggermente appiccicoso.
 Preparare una teglia rettangolare rivestita con carta da forno. Con l'aiuto di un cucchiaio, prelevare poco composto alla volta e adagiarlo sulla teglia creando dei grossi grumi o "bricioloni" frastagliati, mettendoli uno accanto all'altro.
@@ -392,10 +310,6 @@
   </si>
   <si>
     <t>80 gr di fagioli dell'occhio o legumi consentiti; 330 ml di acqua; 165 gr di scarola; Olio extravergine di oliva q.b. Sale marino integrale q.b. Aglio q.b. Bicarbonato q.b.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fagioli dell'occhio; indivia scarola; Olio extravergine di oliva; Sale marino integrale; 
-Aglio; Bicarbonato </t>
   </si>
   <si>
     <t xml:space="preserve">Sciacquare i fagioli dell'occhio sotto acqua corrente, metterli in una ciotola con acqua e un pizzico di bicarbonato e lasciarli in ammollo per 30 minuti. Dopodiché, sciacquarli accuratamente ed eliminare l'acqua in eccesso.
@@ -412,9 +326,6 @@
     <t>200 gr di farina di piselli; 200 gr di tonno in scatola (sgocciolato); Una cipolla bianca piccola (oppure 1 cipollotto), tritata molto finemente; 200 ml di acqua; Olio extravergine di oliva q.b. Sale marino integrale q.b.</t>
   </si>
   <si>
-    <t xml:space="preserve">farina di piselli; tonno; cipolla; Olio extravergine di oliva; Sale marino integrale </t>
-  </si>
-  <si>
     <t>In una scodella capiente, versare la farina di piselli, il sale e la cipolla bianca (o il cipollotto) tritata finissimamente. Mescolare gli ingredienti secchi ed aromatici con l'aiuto di una forchetta.
 Aggiungere il tonno sgranato e un filo di olio extravergine di oliva, continuando a mescolare. Versare i 200 ml di acqua poco alla volta e amalgamare fino a quando l'impasto non risulterà denso e leggermente appiccicoso.
 Con le mani leggermente umide, prelevare un po' di composto alla volta e formare delle piccole polpette, schiacciandole delicatamente tra le mani per dare la forma di focaccine.
@@ -428,9 +339,6 @@
     <t xml:space="preserve">200 gr di agnello tagliato a pezzi; 1 spicchio di aglio tritato; Rametto di rosmarino; Scorza grattugiata di limone q.b.; Olio extravergine d'oliva q.b. Sale marino integrale fino q.b. </t>
   </si>
   <si>
-    <t xml:space="preserve">agnello; aglio; rosmarino; limone; Olio extravergine d'oliva; Sale marino integrale  </t>
-  </si>
-  <si>
     <t>Per preparare l'agnello al forno, iniziare eliminando l'eventuale grasso in eccesso dalla carne e trasferirla all'interno di un contenitore ermetico. Aggiungere un filo d'olio extravergine d'oliva, lo spicchio d'aglio tritato, una spolverata di scorza grattugiata di limone e gli aghi di rosmarino; massaggiare bene la carne con le mani in modo che assorba uniformemente tutti gli aromi. Chiudere il contenitore e lasciar riposare in frigorifero per un tempo compreso tra i 40 minuti e l'ora.
 Trascorso il tempo di marinatura, trasferire i pezzi d'agnello all'interno di una pirofila, irrorare con un ulteriore filo d'olio e cuocere in forno statico preriscaldato a 200 °C per circa 20-25 minuti (evitando la modalità ventilata che asciugherebbe troppo la carne e controllando la doratura dato il peso contenuto).
 A fine cottura, salare a piacere con del sale marino integrale fino, lasciar riposare fuori dal forno per qualche minuto e servire ben caldo.</t>
@@ -441,9 +349,6 @@
   <si>
     <t>180 gr di polpa di agnello (tagliata a pezzi medio-grandi); 150 gr di piselli; 1 cipolla; Olio extravergine di oliva q.b. Sale marino integrale q.b. Rosmarino q.b. Timo q.b. 
 Per il brodo vegetale (a scelta). Con dado: 500 ml di acqua e ½ dado vegetale biologico senza glutammato. Fresco: 500 ml di acqua, ½ carota, ½ costa di sedano, ½ cipolla.</t>
-  </si>
-  <si>
-    <t>Agnello, piselli; cipolla; Olio extravergine di oliva; Sale marino integrale; Rosmarino;Timo; brodo vegetale</t>
   </si>
   <si>
     <t xml:space="preserve">Per prima cosa ci si dedica alla preparazione del brodo vegetale, che servirà ben caldo per la cottura dell'agnello. Si può optare per la versione rapida portando a bollore l'acqua in un pentolino con mezzo dado biologico senza glutammato, oppure preparare un brodo fresco facendo bollire per circa venti minuti mezza carota, mezza costa di sedano e mezza cipolla in mezzo litro d'acqua.
@@ -460,9 +365,6 @@
   <si>
     <t>300 gr di agnello (spalla o cosciotto a pezzi); 150 gr di patate bianche dolci (1 patata grande);  cipolla; 1 spicchio d'aglio; 1 cucchiaio di succo di limone; Olio extravergine d’oliva q.b.
 Origano secco q.b. 1 rametto di rosmarino; Sale marino integrale q.b. Carta da forno e foglio d'alluminio (per la chiusura a cartoccio)</t>
-  </si>
-  <si>
-    <t>Agnello; patate bianche dolci; cipolla; aglio; succo di limone; Olio extravergine d’oliva; Origano; rosmarino; Sale marino integrale</t>
   </si>
   <si>
     <t xml:space="preserve">Disporre i pezzi di agnello all'interno di una ciotola capiente e condirli con un filo d'olio extravergine d'oliva, il succo di limone, lo spicchio d'aglio schiacciato, una generosa spolverata di origano e un pizzico di sale marino integrale, massaggiando accuratamente la carne con le mani per distribuire bene la marinatura.
@@ -479,9 +381,6 @@
   </si>
   <si>
     <t>300 gr di costolette d’agnello giovane; 1 spicchio d’aglio; 2 rametti di rosmarino; 2 cucchiai d’olio extravergine di oliva; sale marino integrale q.b; ½ bicchiere di vino bianco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">costolette d’agnello giovane; aglio; rosmarino; olio extravergine di oliva; sale marino integralevino bianco  </t>
   </si>
   <si>
     <t>Sciacquare accuratamente le costolette d’agnello sotto l’acqua corrente, quindi trasferirle in una ciotola capiente riempita d'acqua con l'aggiunta di meno di mezzo bicchiere d’aceto lasciandole in ammollo per circa 10 minuti per attenuare il sapore forte della carne.
@@ -499,9 +398,6 @@
     <t>300 gr di agnello (coscia o spalla); 1 cipolla; 1 carota; 2 rametti di rosmarino; Sale marino integrale q.b; Olio extravergine q.b.</t>
   </si>
   <si>
-    <t xml:space="preserve">agnello; cipolla; carota; rosmarino; Sale marino integrale; Olio extravergine  </t>
-  </si>
-  <si>
     <t>Sfogliare e affettare la cipolla. Irrorare con un filo di olio il fondo di un tegame a bordi alti. Disporre la cipolla sul fondo e i pezzi carne. Aggiungere i rametti di rosmarino e far rosolare fino a quando la carne risulta leggermente dorata. Pelare la carota e tagliarla a rondelle spesse di mezzo cm. Versarle nel tegame e mescolare. Sfumare con mezzo bicchiere di vino bianco. Aggiungere acqua sino a coprire la carne, chiudere con un coperchio e far cuocere per 20-25 minuti.</t>
   </si>
   <si>
@@ -510,9 +406,6 @@
   <si>
     <t>300 gr di agnello; 200 gr di funghi champignon; 20 ml di vino bianco; 1 cipolla; 1 spicchio di aglio
 Sale marino integrale q.b; Olio extravergine di oliva q.b; 1 rametto di rosmarino; Timo q.b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">agnello;funghi champignon; vino bianco; cipolla; spicchio di aglio; Sale marino integrale; Olio extravergine di oliva; rosmarino; timo  </t>
   </si>
   <si>
     <t xml:space="preserve">In un contenitore mettere la carne, timo, rosmarino, vino e olio extravergine di oliva, mescolare e chiudere il contenitore. Riporre in frigo e lasciare marinare per un’ora.
@@ -529,9 +422,6 @@
 1 rametto di rosmarino; Sale marino q.b; Olio extravergine di oliva q.b</t>
   </si>
   <si>
-    <t>Agnello; pomodoro; alloro; aglio; rosmarino; Sale marino q.b; Olio extravergine di oliva q.b</t>
-  </si>
-  <si>
     <t>Disporre i tocchetti di polpa d'agnello in un contenitore insieme alla foglia di alloro, al rametto di rosmarino e allo spicchio d'aglio schiacciato; coprire a filo con acqua fredda e lasciar marinare in frigorifero per circa 1 ora.
 Trascorso il tempo di marinatura, scolare la carne, asciugarla bene con carta assorbente e rimuovere gli odori dell'ammollo.
 In un tegame o pentola antiaderente, scaldare un filo d'olio extravergine d'oliva con la cipolla tritata. Aggiungere i pezzi di agnello e rosolarli a fiamma medio-alta girandoli spesso, finché non risulteranno ben dorati su tutti i lati.  
@@ -543,10 +433,6 @@
   <si>
     <t>180 gr di carne di agnello (preferibilmente coscia, già privata del grasso in eccesso e della pellicina); 240–250 ml di passata di pomodoro (circa 1 bicchiere e mezzo); 1 carota sbucciata; 
 1 gambo di sedano lavato; ¼ di cipolla; 2 cucchiai di vino bianco; Olio extravergine di oliva q.b; 
-Sale fino q.b.</t>
-  </si>
-  <si>
-    <t>Agnello; passata di pomodoro; sedano; cipolla; vino bianco; Olio extravergine di oliva q.b; 
 Sale fino q.b.</t>
   </si>
   <si>
@@ -561,9 +447,6 @@
   </si>
   <si>
     <t>180 gr di animelle di vitello; 4 carciofi; 1/2 limone; 1 spicchio d’aglio; Un rametto di prezzemolo; Un cucchiaio di vino bianco; Olio extravergine d’oliva q.b; Sale marino integrale q.b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Animelle di vitello; carciofi;  limone; aglio; prezzemolo; vino bianco; Olio extravergine d’oliva ; Sale marino integrale </t>
   </si>
   <si>
     <t xml:space="preserve">Mettere le animelle in acqua fredda per 30-40, cambiando l’acqua tre di volte. Questo procedimento serve ad eliminare i residui di sangue.
@@ -599,9 +482,6 @@
 Un rametto di prezzemolo; Due cucchiai di vino bianco; Sale marino q.b; Olio extravergine di oliva q.b.</t>
   </si>
   <si>
-    <t xml:space="preserve">Animelle; funghi; aglio; alloro; Mezzo limone; prezzemolo; vino bianco; Sale marino; Olio extravergine di oliva </t>
-  </si>
-  <si>
     <t>Iniziare immergendo le animelle in una ciotola con acqua fredda per circa mezz'ora, cambiando l'acqua un paio di volte per spurgarle da eventuali residui di sangue. Nel frattempo, portare a bollore una piccola pentola d'acqua insieme alla foglia di alloro, succo di limone e tuffarvi le animelle e lasciarle sbianchire per circa tre o quattro minuti. Se il limone è biologico si può mettere metà limone, dopo averne spremuto il succo. Scolarle, farle intiepidire e procedere eliminando delicatamente la pellicina trasparente che le riveste e le parti di grasso in eccesso, per poi ridurle a bocconcini o fettine regolari.
 Passare quindi alla preparazione dei funghi Pleurotus, pulendoli accuratamente con un panno umido senza lavarli direttamente sotto l'acqua, e tagliandoli a striscioline oppure sfilacciandoli a mano seguendo la venatura naturale.
 Scaldare un generoso giro d'olio extravergine d'oliva in un'ampia padella antiaderente insieme allo spicchio d'aglio schiacciato e i gambi di prezzemolo. Unire i funghi e saltarli a fiamma medio-alta per cinque o sei minuti, finché non risulteranno ben dorati e avranno riassorbito la loro acqua di</t>
@@ -614,9 +494,6 @@
 4 pomodori secchi sott'olio; Un cucchiaio di mandorle a lamelle o tritate; 2 cucchiai di olio extravergine d'oliva o di vinacciolo; Sale marino q.b. 1 cucchiaino di succo di limone</t>
   </si>
   <si>
-    <t>manzo;  rucola fresca; pomodori secchi; mandorle; olio extravergine d'oliva; olio di vinacciolo; Sale marino; limone</t>
-  </si>
-  <si>
     <t>Disporre le fette sottili di carpaccio di manzo su un piatto da portata, distribuendole in modo uniforme senza sovrapporle eccessivamente. Salare leggermente la carne, per poi condirla con un filo d'olio extravergine d'oliva.
 Tagliare i pomodori secchi a listarelle sottili o a pezzetti. Se si utilizzano mandorle intere, tritarle grossolanamente oppure tostare leggermente in una padellina antiaderente le mandorle già a lamelle per un paio di minuti, finché non risulteranno dorate e fragranti.
 Lavare e asciugare con cura la rucola, quindi distribuirla generosamente sopra la superficie della carne. Aggiungere i pomodori secchi a listarelle e completare con le lamelle di mandorle tostate per dare croccantezza al piatto. Rifinire con un ultimo giro di olio extravergine d'oliva a crudo e, a piacere, qualche goccia di succo di limone.</t>
@@ -629,9 +506,6 @@
 Per la Vinaigrette: 1 cucchiaio di succo di limone; 3 cucchiai di olio extravergine d'oliva o di vinacciolo; Sale marino q.b.</t>
   </si>
   <si>
-    <t xml:space="preserve">manzo; succo di limone; olio extravergine d'oliva; olio di vinacciolo; Sale marino </t>
-  </si>
-  <si>
     <t>Disporre le fettine di carne in una pirofila cercando di non sovrapporle troppo. Irrorare uniformemente la carne con i due cucchiai di succo di limone, coprire la pirofila con della pellicola trasparente e lasciar marinare in frigorifero per circa 15-20 minuti.
 Nel frattempo, preparare la vinaigrette versando in una ciotolina un cucchiaio di succo di limone insieme a un pizzico di sale, mescolando bene fino a scioglierlo completamente. Unire i tre cucchiai di olio extravergine d'oliva e spolverare con del pepe nero macinato al momento, emulsionando energicamente il tutto con una forchetta o una frusta a mano fino a ottenere una salsa omogenea.
 Trascorso il tempo di marinatura, riprendere la carne, disporla sul piatto da portata e completare il piatto versandovi sopra la vinaigrette appena preparata prima di servire.</t>
@@ -644,9 +518,6 @@
 1 cucchiaio di succo di limone; 3 cucchiai di olio extravergine d'oliva o olio di vinacciolo; Sale marino integrale q.b.</t>
   </si>
   <si>
-    <t xml:space="preserve">manzo; cipolla di Tropea; 4-5 gherigli di noci; limone; olio extravergine d'oliva o olio di vinacciolo; Sale marino integrale </t>
-  </si>
-  <si>
     <t>Tritare finemente la cipolla di Tropea e sminuzzando i gherigli di noci, tenendone da parte qualcuno a pezzetti più grandi per la decorazione finale.
 Passare alla preparazione della vinaigrette versando in una ciotolina il cucchiaio di succo di limone insieme al sale marino integrale, mescolando fino a far sciogliere completamente i granelli. Unire i tre cucchiai di olio extravergine d'oliva (o di vinacciolo) ed emulsionare con una forchetta. Aggiungere quindi alla base dell'emulsione la cipolla di Tropea tritata e i due gherigli di noci finemente sminuzzati, amalgamando bene il tutto per far insaporire la salsa. Tenere da parte un gheriglio di noci per decorare. Disporre le fettine di carpaccio di manzo su un piatto da portata, distribuendole in modo uniforme. Nappare la carne versandovi sopra la vinaigrette alle noci e cipolla, completare distribuendo i restanti gherigli di noci sulla superficie per dare croccantezza e servire subito.</t>
   </si>
@@ -655,9 +526,6 @@
   </si>
   <si>
     <t>180 gr di fettine di carne di manzo o vitello (circa 2 o 3 fettine sottili); 150 gr di pomodori ciliegino o piccadilly;  1-2 spicchi d'aglio (uno per il ripieno e uno per il fondo di cottura); 2 cucchiai di formaggio pecorino grattugiato; 1/2 bicchiere di vino bianco secco; Un rametto di prezzemolo fresco tritato; Olio extravergine d'oliva q.b; Sale marino q.b.</t>
-  </si>
-  <si>
-    <t>manzo o vitello; pomodori; aglio; 2 cucchiai di formaggio pecorino grattugiato;  vino bianco secco;  prezzemolo fresco ; Olio extravergine d'oliva q.b; Sale marino q.b.</t>
   </si>
   <si>
     <t>Per preparare gli involtini alla pizzaiola, iniziare battendo delicatamente le fettine di carne tra due fogli di carta forno per renderle sottili e omogenee. Stendere la carne su un piano da lavoro e distribuire al centro di ogni fettina un po' di aglio finemente tritato, del prezzemolo e una spolverata di pecorino grattugiato. Arrotolare strettamente ciascuna fettina su se stessa e fissare gli involtini così ottenuti con degli stuzzicadenti o con del filo da cucina per sigillare il ripieno.
@@ -672,9 +540,6 @@
     <t>180 gr di carne di vitello (o manzo) tagliata a bocconcini; 100 gr di salsa di pomodoro o pelati (circa ¼ di confezione da 400 g); 1/2 di cipolla; 1 foglia di alloro; 2 cucchiai di vino; Olio extravergine d'oliva q.b; Sale marino q.b; Acqua q.b.</t>
   </si>
   <si>
-    <t xml:space="preserve">carne di vitello (o manzo); pomodoro; cipolla; alloro; 2 cucchiai di vino; Olio extravergine d'oliva; Sale marino; Acqua; </t>
-  </si>
-  <si>
     <t>Tritare la cipolla. Versare un filo d'olio extravergine d'oliva direttamente sul fondo della pentola a pressione, aggiungere la cipolla tritata e lasciarla soffriggere a fuoco dolce finché non risulterà dorata. Unire i bocconcini di vitello al soffritto e farli rosolare per circa cinque minuti, girandoli di tanto in tanto per sigillare bene la carne su tutti i lati. Aggiungere la foglia di alloro, regolare di sale, quindi versare il vino e proseguire la cottura a fiamma viva fino a farlo evaporare completamente.
 Aggiungere la salsa di pomodoro (o i pelati leggermente schiacciati) e unire tanta acqua quanto basta per coprire a filo tutto il contenuto della pentola. Chiudere bene il coperchio della pentola a pressione, posizionare la valvola e cuocere a fuoco alto fino a quando la pentola non inizierà a fischiare. Da quel momento, abbassare la fiamma al minimo e proseguire la cottura per circa 30-40 minuti. Trascorso questo tempo, far sfiatare completamente il vapore prima di aprire la pentola in sicurezza. Rimuovere il coperchio, riaccendere il fuoco a fiamma moderata e lasciar restringere il sugo per qualche minuto finché non risulterà ben denso e cremoso prima di servire.</t>
   </si>
@@ -684,9 +549,6 @@
   <si>
     <t>180 gr di carne di manzo magrissima e freschissima (filetto o fesa); 1-2 cucchiaini di succo di limone; Una piccola cipolla (meglio se di Tropea o dolce, tritata finemente); 4-5 olive verdi 
 1-2 cucchiai di olio extravergine d'oliva o di vinacciolo; Sale marino; Un misto di rucola e cicoria per contorno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manzo; succo di limone; cipolla;  olive verdi; olio extravergine d'oliva o di vinacciolo; Sale marino; rucola; cicoria </t>
   </si>
   <si>
     <t>Pulire accuratamente il pezzo di carne, eliminando eventuali nervature o residui di grasso superficiali. Battere o tritare finemente la carne a coltello e trasferirla in una ciotola capiente, condendola con un pizzico di sale, il succo di limone e un filo d'olio extravergine d'oliva.
@@ -698,9 +560,6 @@
   </si>
   <si>
     <t>180 gr carne tritata (bovina); 20 gr di pane grattugiato (pane di grano saraceno o di quinoa) o farina di madorle; 1 uovo; 1 spicchio di aglio; 1 rametto prezzemolo; 3 foglie di basilico; 3 pomodori maturi; Sale marino q.b; Olio extravergine di oliva q.b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manzo o vitello; pane di grano saraceno o pane di quinoa; farina di mandorle; uovo; aglio; prezzemolo; basilico; pomodori; Sale marino; Olio extravergine di oliva </t>
   </si>
   <si>
     <t>In una ciotola aggiungere la carne tritata, un pizzico di sale, l'uovo, il pangrattato, mezzo spicchio d'aglio e il prezzemolo finemente tritati. Mescolare tutti gli ingredienti a mano fino a ottenere un composto omogeneo e ben amalgamato. Staccare dei piccoli pezzetti d'impasto e, ruotandoli tra le palme delle mani, formare le polpette della dimensione desiderata, per poi adagiarle su un piatto e lasciarle riposare in frigorifero.
@@ -718,9 +577,6 @@
 1 cucchiaio di olio extravergine d'oliva. (è possibile sostituire il prezzemolo con dello scalogno o della cipolla rossa finemente tritata).</t>
   </si>
   <si>
-    <t xml:space="preserve">ossobuco di vitello; farina di grano saraceno; cipolla; carota; gambo di sedano; aglio;  vino bianco secco; brodo di carne; Olio extravergine d'oliva q.b; Sale marino q.b; prezzemolo fresco; limone; scalogno </t>
-  </si>
-  <si>
     <t>Per preparare l'ossobuco alla milanese, iniziare praticando tre o quattro tagli lungo la pellicina esterna dell'ossobuco per evitare che la carne si arricci durante la cottura. Salare leggermente l'ossobuco e infarinarlo in modo uniforme da entrambi i lati con la farina di grano saraceno, incrollando l'eccesso. Scaldare un bel giro d'olio extravergine d'oliva in una padella capiente (o in un tegame), adagiarvi l'ossobuco e rosolarlo a fiamma medio-alta finché non sarà ben dorato su tutti e due i lati. Prelevare momentaneamente la carne dalla padella e tenerla da parte su un piatto.
 Nella stessa padella con il fondo di cottura, aggiungere il trito di cipolla, carota e sedano, lasciandoli soffriggere a fuoco dolce finché non risulteranno morbidi (unire un paio di cucchiai di acqua calda o di brodo caldo per non far bruciare le verdure). Aggiungere anche lo spicchio d'aglio schiacciato, se gradito.
 Rimettere l'ossobuco nella padella insieme al soffritto, versare il vino bianco e far sfumare l'alcol a fiamma viva. Versare quindi il l’acqua calda o il brodo di carne caldo fino a coprire parzialmente la carne, portare a leggero bollore, coprire con un coperchio e proseguire la cottura a fuoco basso per circa 1 ora e mezza (o finché la carne non risulterà estremamente tenera), aggiungendo altro brodo caldo o acqua calda qualora il fondo si restringesse troppo.
@@ -733,22 +589,115 @@
     <t>180 gr di nervetti di vitello già lessati e puliti (oppure circa 300-350 g di piedino/ginocchio di vitello grezzo con osso); 4-5 carciofini sott'olio (tagliati a spicchi); 6-8 olive verdi; 3-4 pomodori secchi (tagliati a listarelle); 30 gr di rucola fresca; 1-2 cucchiai di succo di limone; 2 cucchiai di olio extravergine d'oliva o di vinacciolo; Sale marino q.b.</t>
   </si>
   <si>
-    <t xml:space="preserve">nervetti di vitello; carciofini; olive verdi; pomodori secchii; rucola fresca; limone; olio extravergine d'oliva o di vinacciolo; Sale marino </t>
-  </si>
-  <si>
     <t>Lessare i nervetti in abbondante acqua salata (eventualmente aromatizzata con alloro, sedano e carota) per circa due ore o due ore e mezza, finché la carne e le parti cartilaginee non risulteranno estremamente tenere. Scolarli, farli intiepidire e tagliarli a listarelle o tocchetti regolari, rimuovendo eventuali residui ossei.
 Sgocciolare i carciofini sott'olio e tagliarli a spicchi. Tagliare a listarelle sottili i pomodori secchi e snocciolare o affettare le olive. Lavare e asciugare accuratamente la rucola fresca.Trasferire i nervetti ormai freddi o intiepiditi all'interno di un'ampia ciotola. Unire i carciofini, le olive, i pomodori secchi e la rucola.
 Condire il tutto versando l'olio extravergine d'oliva, il succo di limone e un pizzico di sale marino. Mescolare delicatamente con due cucchiai per amalgamare bene tutti gli ingredienti e distribuire l'emulsione di condimento, lasciando riposare l'insalata per qualche minuto a temperatura ambiente prima di servire.</t>
   </si>
   <si>
     <t>Tempo</t>
+  </si>
+  <si>
+    <t>Mandorle; Uova di gallina; Mela; Limoni</t>
+  </si>
+  <si>
+    <t>Uova di gallina; Olio extravergine di oliva; Sale</t>
+  </si>
+  <si>
+    <t>Nocciole; Datteri; Uova di gallina; Caffè di cicoria; Cioccolato</t>
+  </si>
+  <si>
+    <t>Fave; Zucchine; Olio extravergine di oliva; Sale</t>
+  </si>
+  <si>
+    <t>Noci; Cioccolato; Uova di gallina</t>
+  </si>
+  <si>
+    <t>Carote; Mandorle; Nocciole; Uova di gallina</t>
+  </si>
+  <si>
+    <t>Mandorle; Uvetta; Uova di gallina</t>
+  </si>
+  <si>
+    <t>Riso; Olio extravergine di oliva; Uova di gallina; Scarola; Tacchino; Sale</t>
+  </si>
+  <si>
+    <t>Yogurt; Ananas; Mandorle; Miele</t>
+  </si>
+  <si>
+    <t>Borlotti freschi; Manzo; Carote; Cipolle; Sedano; Vino bianco; Olio extravergine di oliva; Sale</t>
+  </si>
+  <si>
+    <t>Piselli; Olio extravergine di oliva; Cipolle; Aglio; Sale</t>
+  </si>
+  <si>
+    <t>Fagioli dell’occhio; Scarola; Olio extravergine di oliva; Sale; Aglio</t>
+  </si>
+  <si>
+    <t>Piselli; Tonno pinna gialla; Cipolle; Olio extravergine di oliva; Sale</t>
+  </si>
+  <si>
+    <t>Agnello; Aglio; Rosmarino; Limoni; Olio extravergine di oliva; Sale</t>
+  </si>
+  <si>
+    <t>Agnello; Piselli; Cipolle; Olio extravergine di oliva; Sale; Rosmarino; Timo</t>
+  </si>
+  <si>
+    <t>Agnello; Patate dolci rosse; Cipolle; Aglio; Limoni; Olio extravergine di oliva; Origano; Rosmarino; Sale</t>
+  </si>
+  <si>
+    <t>Agnello; Aglio; Rosmarino; Olio extravergine di oliva; Sale; Vino bianco</t>
+  </si>
+  <si>
+    <t>Agnello; Cipolle; Carote; Rosmarino; Sale; Olio extravergine di oliva</t>
+  </si>
+  <si>
+    <t>Agnello; Funghi champignon; Vino bianco; Cipolle; Aglio; Sale; Olio extravergine di oliva; Rosmarino; Timo</t>
+  </si>
+  <si>
+    <t>Agnello; Pomodoro; Alloro; Aglio; Rosmarino; Sale; Olio extravergine di oliva</t>
+  </si>
+  <si>
+    <t>Agnello; Pomodoro; Carote; Sedano; Cipolle; Vino bianco; Olio extravergine di oliva; Sale</t>
+  </si>
+  <si>
+    <t>Animelle; Carciofi; Limoni; Aglio; Prezzemolo; Vino bianco; Olio extravergine di oliva; Sale</t>
+  </si>
+  <si>
+    <t>Animelle; Funghi champignon; Aglio; Alloro; Limoni; Prezzemolo; Vino bianco; Sale; Olio extravergine di oliva</t>
+  </si>
+  <si>
+    <t>Manzo; Rucola; Pomodoro; Mandorle; Olio extravergine di oliva; Sale; Limoni</t>
+  </si>
+  <si>
+    <t>Manzo; Limoni; Olio extravergine di oliva; Sale</t>
+  </si>
+  <si>
+    <t>Manzo; Cipolle; Noci; Limoni; Olio extravergine di oliva; Sale</t>
+  </si>
+  <si>
+    <t>Manzo; Vitello; Pomodoro; Aglio; Pecorino; Vino bianco; Prezzemolo; Olio extravergine di oliva; Sale</t>
+  </si>
+  <si>
+    <t>Manzo; Vitello; Pomodoro; Cipolle; Alloro; Vino bianco; Olio extravergine di oliva; Sale</t>
+  </si>
+  <si>
+    <t>Manzo; Limoni; Cipolle; Olive verdi; Olio extravergine di oliva; Sale; Rucola; Cicoria</t>
+  </si>
+  <si>
+    <t>Manzo; Vitello; Uova di gallina; Aglio; Prezzemolo; Basilico; Pomodoro; Sale; Olio extravergine di oliva</t>
+  </si>
+  <si>
+    <t>Vitello; Cipolle; Carote; Sedano; Aglio; Vino bianco; Olio extravergine di oliva; Sale; Prezzemolo; Limoni</t>
+  </si>
+  <si>
+    <t>Vitello; Olive verdi; Pomodoro; Rucola; Limoni; Olio extravergine di oliva; Sale</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -767,11 +716,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -808,7 +752,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -825,20 +769,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1107,24 +1045,24 @@
   <dimension ref="A1:G34"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.75" style="11" customWidth="1"/>
+    <col min="1" max="1" width="6.75" style="9" customWidth="1"/>
     <col min="2" max="2" width="27.375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.375" style="1" customWidth="1"/>
     <col min="4" max="4" width="8.375" customWidth="1"/>
     <col min="5" max="5" width="68.125" customWidth="1"/>
-    <col min="6" max="6" width="79.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="86.625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="95.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -1153,11 +1091,11 @@
       <c r="E2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>9</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1165,20 +1103,20 @@
         <v>0</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1186,20 +1124,20 @@
         <v>0</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1207,20 +1145,20 @@
         <v>0</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
+        <v>114</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1228,41 +1166,41 @@
         <v>0</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>27</v>
+        <v>22</v>
+      </c>
+      <c r="F6" t="s">
+        <v>115</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
+      <c r="A7" s="6">
         <v>0</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>31</v>
+        <v>25</v>
+      </c>
+      <c r="F7" t="s">
+        <v>116</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1270,20 +1208,20 @@
         <v>0</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>35</v>
+        <v>28</v>
+      </c>
+      <c r="F8" t="s">
+        <v>117</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1291,544 +1229,544 @@
         <v>0</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" t="s">
+        <v>118</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="9">
+        <v>0</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" t="s">
+        <v>119</v>
+      </c>
+      <c r="G10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="9">
+        <v>0</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" t="s">
+        <v>120</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="3" t="s">
+    </row>
+    <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="9">
+        <v>0</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="C12" s="3"/>
+      <c r="D12" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="11">
-        <v>0</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="F12" t="s">
+        <v>121</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" t="s">
+    </row>
+    <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="9">
+        <v>0</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F10" t="s">
+      <c r="C13" s="3"/>
+      <c r="D13" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G10" t="s">
+      <c r="F13" t="s">
+        <v>117</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="11">
-        <v>0</v>
-      </c>
-      <c r="B11" s="3" t="s">
+    <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="9">
+        <v>0</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="3" t="s">
+      <c r="C14" s="3"/>
+      <c r="D14" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F14" t="s">
+        <v>122</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G11" s="3" t="s">
+    </row>
+    <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="9">
+        <v>0</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="11">
-        <v>0</v>
-      </c>
-      <c r="B12" s="3" t="s">
+      <c r="C15" s="3"/>
+      <c r="D15" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="3" t="s">
+      <c r="F15" t="s">
+        <v>123</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F12" s="3" t="s">
+    </row>
+    <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="9">
+        <v>0</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="C16" s="3"/>
+      <c r="D16" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="11">
-        <v>0</v>
-      </c>
-      <c r="B13" s="3" t="s">
+      <c r="F16" t="s">
+        <v>124</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="3" t="s">
+    </row>
+    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="9">
+        <v>0</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="C17" s="3"/>
+      <c r="D17" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="F17" t="s">
+        <v>125</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="11">
-        <v>0</v>
-      </c>
-      <c r="B14" s="3" t="s">
+    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="9">
+        <v>0</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="3" t="s">
+      <c r="C18" s="5"/>
+      <c r="D18" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="F18" t="s">
+        <v>126</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="11">
-        <v>0</v>
-      </c>
-      <c r="B15" s="3" t="s">
+    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="9">
+        <v>0</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="3" t="s">
+      <c r="C19" s="3"/>
+      <c r="D19" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="E19" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="F19" t="s">
+        <v>127</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="11">
-        <v>0</v>
-      </c>
-      <c r="B16" s="3" t="s">
+    <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="9">
+        <v>0</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="11">
-        <v>0</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="11">
-        <v>0</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="11">
-        <v>0</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="11">
-        <v>0</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E20" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F20" t="s">
+        <v>128</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="9">
+        <v>0</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="5"/>
+      <c r="D21" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F21" t="s">
+        <v>129</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="9">
+        <v>0</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" s="5"/>
+      <c r="D22" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F22" t="s">
+        <v>130</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="9">
+        <v>0</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F23" t="s">
+        <v>131</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="9">
+        <v>0</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" s="5"/>
+      <c r="D24" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F24" t="s">
+        <v>132</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="9">
+        <v>0</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C25" s="3"/>
+      <c r="D25" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F25" t="s">
+        <v>133</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="9">
+        <v>0</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="3"/>
+      <c r="D26" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="F20" s="10" t="s">
+      <c r="F26" t="s">
+        <v>134</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="G20" s="5" t="s">
+    </row>
+    <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="9">
+        <v>0</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="11">
-        <v>0</v>
-      </c>
-      <c r="B21" s="5" t="s">
+      <c r="C27" s="3"/>
+      <c r="D27" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21" s="3" t="s">
+      <c r="F27" t="s">
+        <v>135</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="F21" s="5" t="s">
+    </row>
+    <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="9">
+        <v>0</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="C28" s="5"/>
+      <c r="D28" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" s="5" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="11">
-        <v>0</v>
-      </c>
-      <c r="B22" s="5" t="s">
+      <c r="F28" t="s">
+        <v>136</v>
+      </c>
+      <c r="G28" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" s="3" t="s">
+    </row>
+    <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="9">
+        <v>0</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="C29" s="3"/>
+      <c r="D29" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="F29" t="s">
+        <v>137</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="11">
-        <v>0</v>
-      </c>
-      <c r="B23" s="3" t="s">
+    <row r="30" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="9">
+        <v>0</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E23" s="3" t="s">
+      <c r="C30" s="3"/>
+      <c r="D30" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F30" t="s">
+        <v>138</v>
+      </c>
+      <c r="G30" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="G23" s="3" t="s">
+    </row>
+    <row r="31" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="9">
+        <v>0</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="11">
-        <v>0</v>
-      </c>
-      <c r="B24" s="5" t="s">
+      <c r="C31" s="3"/>
+      <c r="D31" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C24" s="5"/>
-      <c r="D24" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E24" s="5" t="s">
+      <c r="F31" t="s">
+        <v>139</v>
+      </c>
+      <c r="G31" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="F24" s="5" t="s">
+    </row>
+    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="9">
+        <v>0</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="C32" s="3"/>
+      <c r="D32" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" s="3" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="11">
-        <v>0</v>
-      </c>
-      <c r="B25" s="3" t="s">
+      <c r="F32" t="s">
+        <v>140</v>
+      </c>
+      <c r="G32" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E25" s="3" t="s">
+    </row>
+    <row r="33" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="9">
+        <v>0</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="C33" s="3"/>
+      <c r="D33" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="F33" t="s">
+        <v>141</v>
+      </c>
+      <c r="G33" s="3" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="11">
-        <v>0</v>
-      </c>
-      <c r="B26" s="3" t="s">
+    <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="9">
+        <v>0</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E26" s="3" t="s">
+      <c r="C34" s="3"/>
+      <c r="D34" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F34" t="s">
+        <v>142</v>
+      </c>
+      <c r="G34" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="11">
-        <v>0</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="11">
-        <v>0</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C28" s="5"/>
-      <c r="D28" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="11">
-        <v>0</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="11">
-        <v>0</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C30" s="3"/>
-      <c r="D30" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="11">
-        <v>0</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C31" s="3"/>
-      <c r="D31" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="11">
-        <v>0</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C32" s="3"/>
-      <c r="D32" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="11">
-        <v>0</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C33" s="3"/>
-      <c r="D33" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="11">
-        <v>0</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C34" s="3"/>
-      <c r="D34" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/ricette.xlsx
+++ b/ricette.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Progetti_App\diete_gruppo_sanguigno\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CA7F06A-200F-46C5-B152-1AB81D3A04A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92E99826-DACE-4862-BF90-C78861008B0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -43,9 +43,6 @@
   </si>
   <si>
     <t>Preparazione</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pancake alla mela </t>
   </si>
   <si>
     <t>media</t>
@@ -691,6 +688,9 @@
   </si>
   <si>
     <t>Vitello; Olive verdi; Pomodoro; Rucola; Limoni; Olio extravergine di oliva; Sale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pancake alla mela1 </t>
   </si>
 </sst>
 </file>
@@ -1042,7 +1042,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.75" style="9" customWidth="1"/>
@@ -1062,7 +1062,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -1082,20 +1082,20 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>6</v>
+        <v>142</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>111</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1103,20 +1103,20 @@
         <v>0</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>112</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1124,20 +1124,20 @@
         <v>0</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="F4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1145,20 +1145,20 @@
         <v>0</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" t="s">
+        <v>113</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="F5" t="s">
-        <v>114</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1166,20 +1166,20 @@
         <v>0</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="F6" t="s">
-        <v>115</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1187,20 +1187,20 @@
         <v>0</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" t="s">
+        <v>115</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="F7" t="s">
-        <v>116</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1208,20 +1208,20 @@
         <v>0</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" t="s">
+        <v>116</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="F8" t="s">
-        <v>117</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1229,20 +1229,20 @@
         <v>0</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" t="s">
+        <v>117</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="F9" t="s">
-        <v>118</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1250,19 +1250,19 @@
         <v>0</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" t="s">
         <v>33</v>
       </c>
-      <c r="D10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
+        <v>118</v>
+      </c>
+      <c r="G10" t="s">
         <v>34</v>
-      </c>
-      <c r="F10" t="s">
-        <v>119</v>
-      </c>
-      <c r="G10" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1270,20 +1270,20 @@
         <v>0</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" t="s">
+        <v>119</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="F11" t="s">
-        <v>120</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1291,20 +1291,20 @@
         <v>0</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" t="s">
+        <v>120</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="F12" t="s">
-        <v>121</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1312,20 +1312,20 @@
         <v>0</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" t="s">
+        <v>116</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="F13" t="s">
-        <v>117</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1333,20 +1333,20 @@
         <v>0</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E14" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" t="s">
+        <v>121</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="F14" t="s">
-        <v>122</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1354,20 +1354,20 @@
         <v>0</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E15" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" t="s">
+        <v>122</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="F15" t="s">
-        <v>123</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1375,20 +1375,20 @@
         <v>0</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E16" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F16" t="s">
+        <v>123</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="F16" t="s">
-        <v>124</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1396,20 +1396,20 @@
         <v>0</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E17" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" t="s">
+        <v>124</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="F17" t="s">
-        <v>125</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1417,20 +1417,20 @@
         <v>0</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="F18" t="s">
+        <v>125</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="F18" t="s">
-        <v>126</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1438,20 +1438,20 @@
         <v>0</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="F19" t="s">
+        <v>126</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="F19" t="s">
-        <v>127</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1459,20 +1459,20 @@
         <v>0</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E20" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F20" t="s">
+        <v>127</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="F20" t="s">
-        <v>128</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1480,20 +1480,20 @@
         <v>0</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E21" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F21" t="s">
+        <v>128</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="F21" t="s">
-        <v>129</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1501,20 +1501,20 @@
         <v>0</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E22" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F22" t="s">
+        <v>129</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="F22" t="s">
-        <v>130</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1522,20 +1522,20 @@
         <v>0</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C23" s="3"/>
       <c r="D23" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E23" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F23" t="s">
+        <v>130</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="F23" t="s">
-        <v>131</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1543,20 +1543,20 @@
         <v>0</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E24" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F24" t="s">
+        <v>131</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="F24" t="s">
-        <v>132</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1564,20 +1564,20 @@
         <v>0</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E25" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F25" t="s">
+        <v>132</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="F25" t="s">
-        <v>133</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1585,20 +1585,20 @@
         <v>0</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C26" s="3"/>
       <c r="D26" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E26" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F26" t="s">
+        <v>133</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="F26" t="s">
-        <v>134</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1606,20 +1606,20 @@
         <v>0</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C27" s="3"/>
       <c r="D27" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E27" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F27" t="s">
+        <v>134</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="F27" t="s">
-        <v>135</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1627,20 +1627,20 @@
         <v>0</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E28" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F28" t="s">
+        <v>135</v>
+      </c>
+      <c r="G28" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="F28" t="s">
-        <v>136</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1648,20 +1648,20 @@
         <v>0</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E29" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F29" t="s">
+        <v>136</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="F29" t="s">
-        <v>137</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1669,20 +1669,20 @@
         <v>0</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E30" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F30" t="s">
+        <v>137</v>
+      </c>
+      <c r="G30" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="F30" t="s">
-        <v>138</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1690,20 +1690,20 @@
         <v>0</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C31" s="3"/>
       <c r="D31" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E31" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F31" t="s">
+        <v>138</v>
+      </c>
+      <c r="G31" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="F31" t="s">
-        <v>139</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1711,20 +1711,20 @@
         <v>0</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E32" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F32" t="s">
+        <v>139</v>
+      </c>
+      <c r="G32" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="F32" t="s">
-        <v>140</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1732,20 +1732,20 @@
         <v>0</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E33" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F33" t="s">
+        <v>140</v>
+      </c>
+      <c r="G33" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="F33" t="s">
-        <v>141</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1753,20 +1753,25 @@
         <v>0</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E34" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F34" t="s">
+        <v>141</v>
+      </c>
+      <c r="G34" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="F34" t="s">
-        <v>142</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>109</v>
+    </row>
+    <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="9">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/ricette.xlsx
+++ b/ricette.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Progetti_App\diete_gruppo_sanguigno\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92E99826-DACE-4862-BF90-C78861008B0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8AB2BC9-43FF-4D4D-BF63-6DAE2555212E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -690,7 +690,7 @@
     <t>Vitello; Olive verdi; Pomodoro; Rucola; Limoni; Olio extravergine di oliva; Sale</t>
   </si>
   <si>
-    <t xml:space="preserve">Pancake alla mela1 </t>
+    <t>Pancake alla mela</t>
   </si>
 </sst>
 </file>

--- a/ricette.xlsx
+++ b/ricette.xlsx
@@ -470,13 +470,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">70 gr  farina di mandorle;4 uova; 1 mela (grattugiata e ben strizzata); mezza bustina di cremor tartaro; un cucchiaio scorza grattugiata di limone
-</t>
+          <t>70 gr farina di mandorle; 4 uova; 1 mela (grattugiata e ben strizzata); mezza bustina di cremor tartaro; un cucchiaio scorza grattugiata di limone;</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mandorle; Uova di gallina; Mela; Limoni</t>
+          <t>Mandorle; Uova Di Gallina; Mela; Limoni</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -502,12 +501,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150 gr di farina di ceci (denaturata); 150-180 ml di acqua; 2 uova; ½ cucchiaino di bicarbonato di sodio; un pizzico di sale; Olio extravergine di oliva q.b.  </t>
+          <t>150 gr di farina di ceci (denaturata); 150-180 ml di acqua; 2 uova; ½ cucchiaino di bicarbonato di sodio; un pizzico di sale; Olio extravergine di oliva q; b;</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Uova di gallina; Olio extravergine di oliva; Sale</t>
+          <t>Uova Di Gallina; Olio Extravergine Di Oliva; Sale</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -540,7 +539,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nocciole; Datteri; Uova di gallina; Caffè di cicoria; Cioccolato</t>
+          <t>Nocciole; Datteri; Uova Di Gallina; Caffè Di Cicoria; Cioccolato</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -570,12 +569,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>250 gr farina fave; 15 gr cuticola di psillio; 400 ml di acqua tiepida; Due zucchine; 5 gr lievito secco; Una presa di sale marino integrale; Olio extravergine di oliva q.b. Spezie consentite</t>
+          <t>250 gr farina fave; 15 gr cuticola di psillio; 400 ml di acqua tiepida; Due zucchine; 5 gr lievito secco; Una presa di sale marino integrale; Olio extravergine di oliva q; b; Spezie consentite</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fave; Zucchine; Olio extravergine di oliva; Sale</t>
+          <t>Fave; Zucchine; Olio Extravergine Di Oliva; Sale</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -605,12 +604,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">200 gr noci; 35 gr cioccolato fondente; 4 uova; 30 gr di zucchero; 12 pirottini  </t>
+          <t>200 gr noci; 35 gr cioccolato fondente; 4 uova; 30 gr di zucchero; 12 pirottini</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Noci; Cioccolato; Uova di gallina</t>
+          <t>Noci; Cioccolato; Uova Di Gallina</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -640,12 +639,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">300 gr di carote (pesate pulite e pelate); 100 gr di farina di mandorle; 100 gr di granella di nocciole; 80 gr di farina di grano saraceno; 3 uova; ½ cucchiaino (circa 3 gr) di bicarbonato di sodio; Un cucchiaino (circa 6 gr) di cremor tartaro; Aroma di vaniglia q.b. </t>
+          <t>300 gr di carote (pesate pulite e pelate); 100 gr di farina di mandorle; 100 gr di granella di nocciole; 80 gr di farina di grano saraceno; 3 uova; ½ cucchiaino (circa 3 gr) di bicarbonato di sodio; Un cucchiaino (circa 6 gr) di cremor tartaro; Aroma di vaniglia q; b;</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Carote; Mandorle; Nocciole; Uova di gallina</t>
+          <t>Carote; Mandorle; Nocciole; Uova Di Gallina</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -679,7 +678,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mandorle; Uvetta; Uova di gallina</t>
+          <t>Mandorle; Uvetta; Uova Di Gallina</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -709,13 +708,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>300 gr farina di riso; Sale marino integrale q.b. Un cucchiaio di olio extravergine di oliva; 250 ml d'acqua
-Tre uova; 200 gr scarola; 200 gr tacchino a fette sottili (affettato o fesa arrostita)</t>
+          <t>300 gr farina di riso; Sale marino integrale q; b; Un cucchiaio di olio extravergine di oliva; 250 ml d'acqua; Tre uova; 200 gr scarola; 200 gr tacchino a fette sottili (affettato o fesa arrostita)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Riso; Olio extravergine di oliva; Uova di gallina; Scarola; Tacchino; Sale</t>
+          <t>Riso; Olio Extravergine Di Oliva; Uova Di Gallina; Scarola; Tacchino; Sale</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -776,14 +774,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">75 gr di fagioli borlotti freschi (o altri legumi consentiti); 250 gr di macinato di manzo; Una carota e mezza
-½ cipolla; Sedano q.b. 75 ml di vino bianco; Olio extravergine di oliva q.b. Sale marino integrale q.b.
-Bicarbonato </t>
+          <t>75 gr di fagioli borlotti freschi (o altri legumi consentiti); 250 gr di macinato di manzo; Una carota e mezza; ½ cipolla; Sedano q; b; 75 ml di vino bianco; Olio extravergine di oliva q; b; Sale marino integrale q; b; Bicarbonato</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Borlotti freschi; Manzo; Carote; Cipolle; Sedano; Vino bianco; Olio extravergine di oliva; Sale</t>
+          <t>Borlotti Freschi; Manzo; Carote; Cipolle; Sedano; Vino Bianco; Olio Extravergine Di Oliva; Sale</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -813,13 +809,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">200 gr di farina di piselli; 200 ml di acqua; Olio extravergine di oliva q.b. Cipolla in polvere (oppure cipolla fresca tritata finissimamente) q.b. Aglio in polvere q.b. Sale marino integrale q.b.
-</t>
+          <t>200 gr di farina di piselli; 200 ml di acqua; Olio extravergine di oliva q; b; Cipolla in polvere (oppure cipolla fresca tritata finissimamente) q; b; Aglio in polvere q; b; Sale marino integrale q; b;</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Piselli; Olio extravergine di oliva; Cipolle; Aglio; Sale</t>
+          <t>Piselli; Olio Extravergine Di Oliva; Cipolle; Aglio; Sale</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -849,12 +844,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">180 gr di farina di mandorle; 190 gr di farina di amaranto; 80 gr di uvetta sultanina; 5 uova intere </t>
+          <t>180 gr di farina di mandorle; 190 gr di farina di amaranto; 80 gr di uvetta sultanina; 5 uova intere</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mandorle; Uvetta; Uova di gallina</t>
+          <t>Mandorle; Uvetta; Uova Di Gallina</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -884,12 +879,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>80 gr di fagioli dell'occhio o legumi consentiti; 330 ml di acqua; 165 gr di scarola; Olio extravergine di oliva q.b. Sale marino integrale q.b. Aglio q.b. Bicarbonato q.b.</t>
+          <t>80 gr di fagioli dell'occhio o legumi consentiti; 330 ml di acqua; 165 gr di scarola; Olio extravergine di oliva q; b; Sale marino integrale q; b; Aglio q; b; Bicarbonato q; b;</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fagioli dell’occhio; Scarola; Olio extravergine di oliva; Sale; Aglio</t>
+          <t>Fagioli Dell’occhio; Scarola; Olio Extravergine Di Oliva; Sale; Aglio</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -920,12 +915,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>200 gr di farina di piselli; 200 gr di tonno in scatola (sgocciolato); Una cipolla bianca piccola (oppure 1 cipollotto), tritata molto finemente; 200 ml di acqua; Olio extravergine di oliva q.b. Sale marino integrale q.b.</t>
+          <t>200 gr di farina di piselli; 200 gr di tonno in scatola (sgocciolato); Una cipolla bianca piccola (oppure 1 cipollotto); tritata molto finemente; 200 ml di acqua; Olio extravergine di oliva q; b; Sale marino integrale q; b;</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Piselli; Tonno pinna gialla; Cipolle; Olio extravergine di oliva; Sale</t>
+          <t>Piselli; Tonno Pinna Gialla; Cipolle; Olio Extravergine Di Oliva; Sale</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -955,12 +950,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">200 gr di agnello tagliato a pezzi; 1 spicchio di aglio tritato; Rametto di rosmarino; Scorza grattugiata di limone q.b.; Olio extravergine d'oliva q.b. Sale marino integrale fino q.b. </t>
+          <t>200 gr di agnello tagliato a pezzi; 1 spicchio di aglio tritato; Rametto di rosmarino; Scorza grattugiata di limone q; b; Olio extravergine d'oliva q; b; Sale marino integrale fino q; b;</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Agnello; Aglio; Rosmarino; Limoni; Olio extravergine di oliva; Sale</t>
+          <t>Agnello; Aglio; Rosmarino; Limoni; Olio Extravergine Di Oliva; Sale</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -988,13 +983,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>180 gr di polpa di agnello (tagliata a pezzi medio-grandi); 150 gr di piselli; 1 cipolla; Olio extravergine di oliva q.b. Sale marino integrale q.b. Rosmarino q.b. Timo q.b. 
-Per il brodo vegetale (a scelta). Con dado: 500 ml di acqua e ½ dado vegetale biologico senza glutammato. Fresco: 500 ml di acqua, ½ carota, ½ costa di sedano, ½ cipolla.</t>
+          <t>180 gr di polpa di agnello (tagliata a pezzi medio-grandi); 150 gr di piselli; 1 cipolla; Olio extravergine di oliva q; b; Sale marino integrale q; b; Rosmarino q; b; Timo q; b; Per il brodo vegetale (a scelta); Con dado: 500 ml di acqua e ½ dado vegetale biologico senza glutammato; Fresco: 500 ml di acqua; ½ carota; ½ costa di sedano; ½ cipolla;</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Agnello; Piselli; Cipolle; Olio extravergine di oliva; Sale; Rosmarino; Timo</t>
+          <t>Agnello; Piselli; Cipolle; Olio Extravergine Di Oliva; Sale; Rosmarino; Timo</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1023,13 +1017,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>300 gr di agnello (spalla o cosciotto a pezzi); 150 gr di patate bianche dolci (1 patata grande);  cipolla; 1 spicchio d'aglio; 1 cucchiaio di succo di limone; Olio extravergine d’oliva q.b.
-Origano secco q.b. 1 rametto di rosmarino; Sale marino integrale q.b. Carta da forno e foglio d'alluminio (per la chiusura a cartoccio)</t>
+          <t>300 gr di agnello (spalla o cosciotto a pezzi); 150 gr di patate bianche dolci (1 patata grande); cipolla; 1 spicchio d'aglio; 1 cucchiaio di succo di limone; Olio extravergine d’oliva q; b; Origano secco q; b; 1 rametto di rosmarino; Sale marino integrale q; b; Carta da forno e foglio d'alluminio (per la chiusura a cartoccio)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Agnello; Patate dolci rosse; Cipolle; Aglio; Limoni; Olio extravergine di oliva; Origano; Rosmarino; Sale</t>
+          <t>Agnello; Patate Dolci Rosse; Cipolle; Aglio; Limoni; Olio Extravergine Di Oliva; Origano; Rosmarino; Sale</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1059,12 +1052,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>300 gr di costolette d’agnello giovane; 1 spicchio d’aglio; 2 rametti di rosmarino; 2 cucchiai d’olio extravergine di oliva; sale marino integrale q.b; ½ bicchiere di vino bianco</t>
+          <t>300 gr di costolette d’agnello giovane; 1 spicchio d’aglio; 2 rametti di rosmarino; 2 cucchiai d’olio extravergine di oliva; sale marino integrale q; b; ½ bicchiere di vino bianco</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Agnello; Aglio; Rosmarino; Olio extravergine di oliva; Sale; Vino bianco</t>
+          <t>Agnello; Aglio; Rosmarino; Olio Extravergine Di Oliva; Sale; Vino Bianco</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1096,12 +1089,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>300 gr di agnello (coscia o spalla); 1 cipolla; 1 carota; 2 rametti di rosmarino; Sale marino integrale q.b; Olio extravergine q.b.</t>
+          <t>300 gr di agnello (coscia o spalla); 1 cipolla; 1 carota; 2 rametti di rosmarino; Sale marino integrale q; b; Olio extravergine q; b;</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Agnello; Cipolle; Carote; Rosmarino; Sale; Olio extravergine di oliva</t>
+          <t>Agnello; Cipolle; Carote; Rosmarino; Sale; Olio Extravergine Di Oliva</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1127,13 +1120,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>300 gr di agnello; 200 gr di funghi champignon; 20 ml di vino bianco; 1 cipolla; 1 spicchio di aglio
-Sale marino integrale q.b; Olio extravergine di oliva q.b; 1 rametto di rosmarino; Timo q.b</t>
+          <t>300 gr di agnello; 200 gr di funghi champignon; 20 ml di vino bianco; 1 cipolla; 1 spicchio di aglio; Sale marino integrale q; b; Olio extravergine di oliva q; b; 1 rametto di rosmarino; Timo q; b</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Agnello; Funghi champignon; Vino bianco; Cipolle; Aglio; Sale; Olio extravergine di oliva; Rosmarino; Timo</t>
+          <t>Agnello; Funghi Champignon; Vino Bianco; Cipolle; Aglio; Sale; Olio Extravergine Di Oliva; Rosmarino; Timo</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1163,13 +1155,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>200 gr di polpa di agnello; 150-200 ml di passata di pomodoro; 1 foglia di alloro; 1 spicchio di aglio
-1 rametto di rosmarino; Sale marino q.b; Olio extravergine di oliva q.b</t>
+          <t>200 gr di polpa di agnello; 150-200 ml di passata di pomodoro; 1 foglia di alloro; 1 spicchio di aglio; 1 rametto di rosmarino; Sale marino q; b; Olio extravergine di oliva q; b</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Agnello; Pomodoro; Alloro; Aglio; Rosmarino; Sale; Olio extravergine di oliva</t>
+          <t>Agnello; Pomodoro; Alloro; Aglio; Rosmarino; Sale; Olio Extravergine Di Oliva</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1198,14 +1189,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>180 gr di carne di agnello (preferibilmente coscia, già privata del grasso in eccesso e della pellicina); 240–250 ml di passata di pomodoro (circa 1 bicchiere e mezzo); 1 carota sbucciata; 
-1 gambo di sedano lavato; ¼ di cipolla; 2 cucchiai di vino bianco; Olio extravergine di oliva q.b; 
-Sale fino q.b.</t>
+          <t>180 gr di carne di agnello (preferibilmente coscia; già privata del grasso in eccesso e della pellicina); 240–250 ml di passata di pomodoro (circa 1 bicchiere e mezzo); 1 carota sbucciata; 1 gambo di sedano lavato; ¼ di cipolla; 2 cucchiai di vino bianco; Olio extravergine di oliva q; b; Sale fino q; b;</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Agnello; Pomodoro; Carote; Sedano; Cipolle; Vino bianco; Olio extravergine di oliva; Sale</t>
+          <t>Agnello; Pomodoro; Carote; Sedano; Cipolle; Vino Bianco; Olio Extravergine Di Oliva; Sale</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1235,12 +1224,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>180 gr di animelle di vitello; 4 carciofi; 1/2 limone; 1 spicchio d’aglio; Un rametto di prezzemolo; Un cucchiaio di vino bianco; Olio extravergine d’oliva q.b; Sale marino integrale q.b</t>
+          <t>180 gr di animelle di vitello; 4 carciofi; 1/2 limone; 1 spicchio d’aglio; Un rametto di prezzemolo; Un cucchiaio di vino bianco; Olio extravergine d’oliva q; b; Sale marino integrale q; b</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Animelle; Carciofi; Limoni; Aglio; Prezzemolo; Vino bianco; Olio extravergine di oliva; Sale</t>
+          <t>Animelle; Carciofi; Limoni; Aglio; Prezzemolo; Vino Bianco; Olio Extravergine Di Oliva; Sale</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1270,13 +1259,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>180 gr di animelle; 250 gr di funghi; 1 spicchio di aglio; 1 foglia di alloro; Mezzo limone
-Un rametto di prezzemolo; Due cucchiai di vino bianco; Sale marino q.b; Olio extravergine di oliva q.b.</t>
+          <t>180 gr di animelle; 250 gr di funghi; 1 spicchio di aglio; 1 foglia di alloro; Mezzo limone; Un rametto di prezzemolo; Due cucchiai di vino bianco; Sale marino q; b; Olio extravergine di oliva q; b;</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Animelle; Funghi champignon; Aglio; Alloro; Limoni; Prezzemolo; Vino bianco; Sale; Olio extravergine di oliva</t>
+          <t>Animelle; Funghi Champignon; Aglio; Alloro; Limoni; Prezzemolo; Vino Bianco; Sale; Olio Extravergine Di Oliva</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1304,13 +1292,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>180 gr di carpaccio di manzo (fette sottilissime); Una manciata abbondante di rucola fresca; 
-4 pomodori secchi sott'olio; Un cucchiaio di mandorle a lamelle o tritate; 2 cucchiai di olio extravergine d'oliva o di vinacciolo; Sale marino q.b. 1 cucchiaino di succo di limone</t>
+          <t>180 gr di carpaccio di manzo (fette sottilissime); Una manciata abbondante di rucola fresca; 4 pomodori secchi sott'olio; Un cucchiaio di mandorle a lamelle o tritate; 2 cucchiai di olio extravergine d'oliva o di vinacciolo; Sale marino q; b; 1 cucchiaino di succo di limone</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Manzo; Rucola; Pomodoro; Mandorle; Olio extravergine di oliva; Sale; Limoni</t>
+          <t>Manzo; Rucola; Pomodoro; Mandorle; Olio Extravergine Di Oliva; Sale; Limoni</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1338,13 +1325,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>180 gr di carpaccio di manzo (fette sottilissime); 2 cucchiai di succo di limone (per la marinatura)
-Per la Vinaigrette: 1 cucchiaio di succo di limone; 3 cucchiai di olio extravergine d'oliva o di vinacciolo; Sale marino q.b.</t>
+          <t>180 gr di carpaccio di manzo (fette sottilissime); 2 cucchiai di succo di limone (per la marinatura); Per la Vinaigrette: 1 cucchiaio di succo di limone; 3 cucchiai di olio extravergine d'oliva o di vinacciolo; Sale marino q; b;</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Manzo; Limoni; Olio extravergine di oliva; Sale</t>
+          <t>Manzo; Limoni; Olio Extravergine Di Oliva; Sale</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1372,13 +1358,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>180 g di carpaccio di manzo; ½ cipolla di Tropea; 4-5 gherigli di noci; Per la Vinaigrette alle Noci
-1 cucchiaio di succo di limone; 3 cucchiai di olio extravergine d'oliva o olio di vinacciolo; Sale marino integrale q.b.</t>
+          <t>180 g di carpaccio di manzo; ½ cipolla di Tropea; 4-5 gherigli di noci; Per la Vinaigrette alle Noci; 1 cucchiaio di succo di limone; 3 cucchiai di olio extravergine d'oliva o olio di vinacciolo; Sale marino integrale q; b;</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Manzo; Cipolle; Noci; Limoni; Olio extravergine di oliva; Sale</t>
+          <t>Manzo; Cipolle; Noci; Limoni; Olio Extravergine Di Oliva; Sale</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1405,12 +1390,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>180 gr di fettine di carne di manzo o vitello (circa 2 o 3 fettine sottili); 150 gr di pomodori ciliegino o piccadilly;  1-2 spicchi d'aglio (uno per il ripieno e uno per il fondo di cottura); 2 cucchiai di formaggio pecorino grattugiato; 1/2 bicchiere di vino bianco secco; Un rametto di prezzemolo fresco tritato; Olio extravergine d'oliva q.b; Sale marino q.b.</t>
+          <t>180 gr di fettine di carne di manzo o vitello (circa 2 o 3 fettine sottili); 150 gr di pomodori ciliegino o piccadilly; 1-2 spicchi d'aglio (uno per il ripieno e uno per il fondo di cottura); 2 cucchiai di formaggio pecorino grattugiato; 1/2 bicchiere di vino bianco secco; Un rametto di prezzemolo fresco tritato; Olio extravergine d'oliva q; b; Sale marino q; b;</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Manzo; Vitello; Pomodoro; Aglio; Pecorino; Vino bianco; Prezzemolo; Olio extravergine di oliva; Sale</t>
+          <t>Manzo; Vitello; Pomodoro; Aglio; Pecorino; Vino Bianco; Prezzemolo; Olio Extravergine Di Oliva; Sale</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1439,12 +1424,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>180 gr di carne di vitello (o manzo) tagliata a bocconcini; 100 gr di salsa di pomodoro o pelati (circa ¼ di confezione da 400 g); 1/2 di cipolla; 1 foglia di alloro; 2 cucchiai di vino; Olio extravergine d'oliva q.b; Sale marino q.b; Acqua q.b.</t>
+          <t>180 gr di carne di vitello (o manzo) tagliata a bocconcini; 100 gr di salsa di pomodoro o pelati (circa ¼ di confezione da 400 g); 1/2 di cipolla; 1 foglia di alloro; 2 cucchiai di vino; Olio extravergine d'oliva q; b; Sale marino q; b; Acqua q; b;</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Manzo; Vitello; Pomodoro; Cipolle; Alloro; Vino bianco; Olio extravergine di oliva; Sale</t>
+          <t>Manzo; Vitello; Pomodoro; Cipolle; Alloro; Vino Bianco; Olio Extravergine Di Oliva; Sale</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1471,13 +1456,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>180 gr di carne di manzo magrissima e freschissima (filetto o fesa); 1-2 cucchiaini di succo di limone; Una piccola cipolla (meglio se di Tropea o dolce, tritata finemente); 4-5 olive verdi 
-1-2 cucchiai di olio extravergine d'oliva o di vinacciolo; Sale marino; Un misto di rucola e cicoria per contorno</t>
+          <t>180 gr di carne di manzo magrissima e freschissima (filetto o fesa); 1-2 cucchiaini di succo di limone; Una piccola cipolla (meglio se di Tropea o dolce; tritata finemente); 4-5 olive verdi; 1-2 cucchiai di olio extravergine d'oliva o di vinacciolo; Sale marino; Un misto di rucola e cicoria per contorno</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Manzo; Limoni; Cipolle; Olive verdi; Olio extravergine di oliva; Sale; Rucola; Cicoria</t>
+          <t>Manzo; Limoni; Cipolle; Olive Verdi; Olio Extravergine Di Oliva; Sale; Rucola; Cicoria</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1505,12 +1489,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>180 gr carne tritata (bovina); 20 gr di pane grattugiato (pane di grano saraceno o di quinoa) o farina di madorle; 1 uovo; 1 spicchio di aglio; 1 rametto prezzemolo; 3 foglie di basilico; 3 pomodori maturi; Sale marino q.b; Olio extravergine di oliva q.b</t>
+          <t>180 gr carne tritata (bovina); 20 gr di pane grattugiato (pane di grano saraceno o di quinoa) o farina di madorle; 1 uovo; 1 spicchio di aglio; 1 rametto prezzemolo; 3 foglie di basilico; 3 pomodori maturi; Sale marino q; b; Olio extravergine di oliva q; b</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Manzo; Vitello; Uova di gallina; Aglio; Prezzemolo; Basilico; Pomodoro; Sale; Olio extravergine di oliva</t>
+          <t>Manzo; Vitello; Uova Di Gallina; Aglio; Prezzemolo; Basilico; Pomodoro; Sale; Olio Extravergine Di Oliva</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1539,15 +1523,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>350-400 gr di ossobuco di vitello; 2-3 cucchiai di farina di grano saraceno; ½ cipolla media (tritata)
-½ carota (tritata); ½ gambo di sedano (tritato); 1 spicchio d'aglio (facoltativo); 100 ml di vino bianco secco; 300-400 ml di acqua calda o brodo di carne; Olio extravergine d'oliva q.b; Sale marino q.b
-Per la gremolata. 15 gr di prezzemolo fresco (foglie e gambi tritati); 1 spicchio d'aglio sbucciato (tritato finissimo); La scorza grattugiata di 1 limone biologico; 1 cucchiaino di succo di limone
-1 cucchiaio di olio extravergine d'oliva. (è possibile sostituire il prezzemolo con dello scalogno o della cipolla rossa finemente tritata).</t>
+          <t>350-400 gr di ossobuco di vitello; 2-3 cucchiai di farina di grano saraceno; ½ cipolla media (tritata); ½ carota (tritata); ½ gambo di sedano (tritato); 1 spicchio d'aglio (facoltativo); 100 ml di vino bianco secco; 300-400 ml di acqua calda o brodo di carne; Olio extravergine d'oliva q; b; Sale marino q; b; Per la gremolata; 15 gr di prezzemolo fresco (foglie e gambi tritati); 1 spicchio d'aglio sbucciato (tritato finissimo); La scorza grattugiata di 1 limone biologico; 1 cucchiaino di succo di limone; 1 cucchiaio di olio extravergine d'oliva; (è possibile sostituire il prezzemolo con dello scalogno o della cipolla rossa finemente tritata);</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitello; Cipolle; Carote; Sedano; Aglio; Vino bianco; Olio extravergine di oliva; Sale; Prezzemolo; Limoni</t>
+          <t>Vitello; Cipolle; Carote; Sedano; Aglio; Vino Bianco; Olio Extravergine Di Oliva; Sale; Prezzemolo; Limoni</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1576,12 +1557,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>180 gr di nervetti di vitello già lessati e puliti (oppure circa 300-350 g di piedino/ginocchio di vitello grezzo con osso); 4-5 carciofini sott'olio (tagliati a spicchi); 6-8 olive verdi; 3-4 pomodori secchi (tagliati a listarelle); 30 gr di rucola fresca; 1-2 cucchiai di succo di limone; 2 cucchiai di olio extravergine d'oliva o di vinacciolo; Sale marino q.b.</t>
+          <t>180 gr di nervetti di vitello già lessati e puliti (oppure circa 300-350 g di piedino/ginocchio di vitello grezzo con osso); 4-5 carciofini sott'olio (tagliati a spicchi); 6-8 olive verdi; 3-4 pomodori secchi (tagliati a listarelle); 30 gr di rucola fresca; 1-2 cucchiai di succo di limone; 2 cucchiai di olio extravergine d'oliva o di vinacciolo; Sale marino q; b;</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitello; Olive verdi; Pomodoro; Rucola; Limoni; Olio extravergine di oliva; Sale</t>
+          <t>Vitello; Olive Verdi; Pomodoro; Rucola; Limoni; Olio Extravergine Di Oliva; Sale</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1611,12 +1592,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>150 g di farina di grano saraceno; 2 uova; 75 ml di acqua; 140 g di mela (circa una mela media); 1 pizzico di sale; 1/2 cucchiaino di zenzero in polvere; 2 g di bicarbonato; poco olio per la padella (es; Olio di vinaccioli o evo)</t>
+          <t>150 g di farina di grano saraceno; 2 uova; 75 ml di acqua; 140 g di mela (circa una mela media); 1 pizzico di sale; 1/2 cucchiaino di zenzero in polvere; 2 g di bicarbonato; poco olio per la padella (es; Olio di vinaccioli o evo); Grano Saraceno; Uova; Mela; Zenzero; Bicarbonato</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grano Saraceno Uova Mela Zenzero Bicarbonato</t>
+          <t>Grano; Saraceno; Uova; Mela; Zenzero; Bicarbonato</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">

--- a/ricette.xlsx
+++ b/ricette.xlsx
@@ -475,7 +475,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mandorle; Uova Di Gallina; Mela; Limoni</t>
+          <t>Mandorle; Uova di Gallina; Mela; Limoni</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -506,7 +506,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Uova Di Gallina; Olio Extravergine Di Oliva; Sale</t>
+          <t>Uova di Gallina; Olio Extravergine di Oliva; Sale</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nocciole; Datteri; Uova Di Gallina; Caffè Di Cicoria; Cioccolato</t>
+          <t>Nocciole; Datteri; Uova di Gallina; Caffè di Cicoria; Cioccolato</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fave; Zucchine; Olio Extravergine Di Oliva; Sale</t>
+          <t>Fave; Zucchine; Olio Extravergine di Oliva; Sale</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Noci; Cioccolato; Uova Di Gallina</t>
+          <t>Noci; Cioccolato; Uova di Gallina</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Carote; Mandorle; Nocciole; Uova Di Gallina</t>
+          <t>Carote; Mandorle; Nocciole; Uova di Gallina</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mandorle; Uvetta; Uova Di Gallina</t>
+          <t>Mandorle; Uvetta; Uova di Gallina</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Riso; Olio Extravergine Di Oliva; Uova Di Gallina; Scarola; Tacchino; Sale</t>
+          <t>Riso; Olio Extravergine di Oliva; Uova di Gallina; Scarola; Tacchino; Sale</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Borlotti Freschi; Manzo; Carote; Cipolle; Sedano; Vino Bianco; Olio Extravergine Di Oliva; Sale</t>
+          <t>Borlotti Freschi; Manzo; Carote; Cipolle; Sedano; Vino Bianco; Olio Extravergine di Oliva; Sale</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Piselli; Olio Extravergine Di Oliva; Cipolle; Aglio; Sale</t>
+          <t>Piselli; Olio Extravergine di Oliva; Cipolle; Aglio; Sale</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mandorle; Uvetta; Uova Di Gallina</t>
+          <t>Mandorle; Uvetta; Uova di Gallina</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fagioli Dell’occhio; Scarola; Olio Extravergine Di Oliva; Sale; Aglio</t>
+          <t>Fagioli Dell’occhio; Scarola; Olio Extravergine di Oliva; Sale; Aglio</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Piselli; Tonno Pinna Gialla; Cipolle; Olio Extravergine Di Oliva; Sale</t>
+          <t>Piselli; Tonno Pinna Gialla; Cipolle; Olio Extravergine di Oliva; Sale</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Agnello; Aglio; Rosmarino; Limoni; Olio Extravergine Di Oliva; Sale</t>
+          <t>Agnello; Aglio; Rosmarino; Limoni; Olio Extravergine di Oliva; Sale</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Agnello; Piselli; Cipolle; Olio Extravergine Di Oliva; Sale; Rosmarino; Timo</t>
+          <t>Agnello; Piselli; Cipolle; Olio Extravergine di Oliva; Sale; Rosmarino; Timo</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Agnello; Patate Dolci Rosse; Cipolle; Aglio; Limoni; Olio Extravergine Di Oliva; Origano; Rosmarino; Sale</t>
+          <t>Agnello; Patate Dolci Rosse; Cipolle; Aglio; Limoni; Olio Extravergine di Oliva; Origano; Rosmarino; Sale</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Agnello; Aglio; Rosmarino; Olio Extravergine Di Oliva; Sale; Vino Bianco</t>
+          <t>Agnello; Aglio; Rosmarino; Olio Extravergine di Oliva; Sale; Vino Bianco</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Agnello; Cipolle; Carote; Rosmarino; Sale; Olio Extravergine Di Oliva</t>
+          <t>Agnello; Cipolle; Carote; Rosmarino; Sale; Olio Extravergine di Oliva</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Agnello; Funghi Champignon; Vino Bianco; Cipolle; Aglio; Sale; Olio Extravergine Di Oliva; Rosmarino; Timo</t>
+          <t>Agnello; Funghi Champignon; Vino Bianco; Cipolle; Aglio; Sale; Olio Extravergine di Oliva; Rosmarino; Timo</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Agnello; Pomodoro; Alloro; Aglio; Rosmarino; Sale; Olio Extravergine Di Oliva</t>
+          <t>Agnello; Pomodoro; Alloro; Aglio; Rosmarino; Sale; Olio Extravergine di Oliva</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Agnello; Pomodoro; Carote; Sedano; Cipolle; Vino Bianco; Olio Extravergine Di Oliva; Sale</t>
+          <t>Agnello; Pomodoro; Carote; Sedano; Cipolle; Vino Bianco; Olio Extravergine di Oliva; Sale</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Animelle; Carciofi; Limoni; Aglio; Prezzemolo; Vino Bianco; Olio Extravergine Di Oliva; Sale</t>
+          <t>Animelle; Carciofi; Limoni; Aglio; Prezzemolo; Vino Bianco; Olio Extravergine di Oliva; Sale</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Animelle; Funghi Champignon; Aglio; Alloro; Limoni; Prezzemolo; Vino Bianco; Sale; Olio Extravergine Di Oliva</t>
+          <t>Animelle; Funghi Champignon; Aglio; Alloro; Limoni; Prezzemolo; Vino Bianco; Sale; Olio Extravergine di Oliva</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Manzo; Rucola; Pomodoro; Mandorle; Olio Extravergine Di Oliva; Sale; Limoni</t>
+          <t>Manzo; Rucola; Pomodoro; Mandorle; Olio Extravergine di Oliva; Sale; Limoni</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Manzo; Limoni; Olio Extravergine Di Oliva; Sale</t>
+          <t>Manzo; Limoni; Olio Extravergine di Oliva; Sale</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Manzo; Cipolle; Noci; Limoni; Olio Extravergine Di Oliva; Sale</t>
+          <t>Manzo; Cipolle; Noci; Limoni; Olio Extravergine di Oliva; Sale</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Manzo; Vitello; Pomodoro; Aglio; Pecorino; Vino Bianco; Prezzemolo; Olio Extravergine Di Oliva; Sale</t>
+          <t>Manzo; Vitello; Pomodoro; Aglio; Pecorino; Vino Bianco; Prezzemolo; Olio Extravergine di Oliva; Sale</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Manzo; Vitello; Pomodoro; Cipolle; Alloro; Vino Bianco; Olio Extravergine Di Oliva; Sale</t>
+          <t>Manzo; Vitello; Pomodoro; Cipolle; Alloro; Vino Bianco; Olio Extravergine di Oliva; Sale</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Manzo; Limoni; Cipolle; Olive Verdi; Olio Extravergine Di Oliva; Sale; Rucola; Cicoria</t>
+          <t>Manzo; Limoni; Cipolle; Olive Verdi; Olio Extravergine di Oliva; Sale; Rucola; Cicoria</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Manzo; Vitello; Uova Di Gallina; Aglio; Prezzemolo; Basilico; Pomodoro; Sale; Olio Extravergine Di Oliva</t>
+          <t>Manzo; Vitello; Uova di Gallina; Aglio; Prezzemolo; Basilico; Pomodoro; Sale; Olio Extravergine di Oliva</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitello; Cipolle; Carote; Sedano; Aglio; Vino Bianco; Olio Extravergine Di Oliva; Sale; Prezzemolo; Limoni</t>
+          <t>Vitello; Cipolle; Carote; Sedano; Aglio; Vino Bianco; Olio Extravergine di Oliva; Sale; Prezzemolo; Limoni</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitello; Olive Verdi; Pomodoro; Rucola; Limoni; Olio Extravergine Di Oliva; Sale</t>
+          <t>Vitello; Olive Verdi; Pomodoro; Rucola; Limoni; Olio Extravergine di Oliva; Sale</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grano; Saraceno; Uova; Mela; Zenzero; Bicarbonato</t>
+          <t>Grano Saraceno; Uova; Mela; Zenzero; Bicarbonato</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
